--- a/outputs/daily/hr_rankings_2026-10-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-14.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.9</v>
+        <v>58.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>50.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -905,14 +905,14 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>5</t>
@@ -930,12 +930,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.2</v>
+        <v>54.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
@@ -1209,13 +1209,13 @@
         <v>50.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -1223,17 +1223,17 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1275,22 +1275,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1300,72 +1300,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.1</v>
+        <v>54.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,11 +1514,11 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
@@ -1527,13 +1527,13 @@
         <v>50.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -1541,17 +1541,17 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1593,22 +1593,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1618,72 +1618,72 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.7</v>
+        <v>51.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,11 +1832,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
@@ -1845,13 +1845,13 @@
         <v>50.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1859,17 +1859,17 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1911,22 +1911,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1941,67 +1941,67 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
@@ -2163,13 +2163,13 @@
         <v>50.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2177,17 +2177,17 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2229,27 +2229,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2259,67 +2259,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,11 +2468,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
@@ -2481,13 +2481,13 @@
         <v>50.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2495,17 +2495,17 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2552,22 +2552,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2577,67 +2577,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3041,22 +3041,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>45.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3104,44 +3104,46 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
         <v>50.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>57</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3156,12 +3158,12 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -3183,12 +3185,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3198,12 +3200,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3213,102 +3215,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3342,16 +3344,56 @@
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Park/split help but hitter sheet not loud</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3359,12 +3401,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3384,12 +3426,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3408,7 +3450,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3422,11 +3464,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -3435,13 +3477,13 @@
         <v>50.1</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3459,7 +3501,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3506,22 +3548,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3531,67 +3573,67 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -3626,7 +3668,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3677,24 +3719,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -3702,22 +3744,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3726,7 +3768,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3740,33 +3782,31 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>33.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>50.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T11" t="n">
+        <v>78</v>
+      </c>
+      <c r="U11" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="V11" t="n">
         <v>50</v>
       </c>
-      <c r="U11" t="n">
-        <v>12</v>
-      </c>
-      <c r="V11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>57</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>No</t>
@@ -3779,7 +3819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -3821,154 +3861,154 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Last 7 games: 6/24, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>7.87</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>45.42</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>90.54</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>101.6393</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.4266</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.1702</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.3322</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>73.41</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>36.51</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>36.04</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>21.26</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>83.89</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.2559</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.0609</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>37.53</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>88.98</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>98.7109</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>0.1598</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>0.3433</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>71.58</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>20.59</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>42.96</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>0.1658</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>8.65</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>37.12</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>88.27</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.3953</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.1607</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN11" t="inlineStr">
         <is>
           <t>72</t>
@@ -3980,56 +4020,16 @@
         </is>
       </c>
       <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4749,7 +4749,7 @@
         <v>50.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4763,14 +4763,14 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>9</t>
@@ -4788,12 +4788,12 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.4</v>
+        <v>38.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5067,7 +5067,7 @@
         <v>50.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -5081,14 +5081,14 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>8</t>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.9</v>
+        <v>58.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +7063,7 @@
         <v>50.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -7077,14 +7077,14 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>5</t>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.2</v>
+        <v>54.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7368,11 +7368,11 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
@@ -7381,13 +7381,13 @@
         <v>50.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -7395,17 +7395,17 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -7447,22 +7447,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -7472,72 +7472,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.1</v>
+        <v>54.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7686,11 +7686,11 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
@@ -7699,13 +7699,13 @@
         <v>50.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -7713,17 +7713,17 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -7765,22 +7765,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -7790,72 +7790,72 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.7</v>
+        <v>51.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8004,11 +8004,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
@@ -8017,13 +8017,13 @@
         <v>50.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -8031,17 +8031,17 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -8083,22 +8083,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -8113,67 +8113,67 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8322,11 +8322,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
@@ -8335,13 +8335,13 @@
         <v>50.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8349,17 +8349,17 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -8401,27 +8401,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8431,67 +8431,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8640,11 +8640,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
@@ -8653,13 +8653,13 @@
         <v>50.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8667,17 +8667,17 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -8724,22 +8724,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8749,67 +8749,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9213,22 +9213,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9238,22 +9238,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>45.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9276,44 +9276,46 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
         <v>50.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>57</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -9328,12 +9330,12 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -9355,12 +9357,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -9370,12 +9372,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9385,102 +9387,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9514,16 +9516,56 @@
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Park/split help but hitter sheet not loud</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9531,12 +9573,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9556,12 +9598,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9580,7 +9622,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9594,11 +9636,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -9607,13 +9649,13 @@
         <v>50.1</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9631,7 +9673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -9678,22 +9720,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9703,67 +9745,67 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9798,7 +9840,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9849,24 +9891,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -9874,22 +9916,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9898,7 +9940,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9912,33 +9954,31 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>33.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>50.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T11" t="n">
+        <v>78</v>
+      </c>
+      <c r="U11" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="V11" t="n">
         <v>50</v>
       </c>
-      <c r="U11" t="n">
-        <v>12</v>
-      </c>
-      <c r="V11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>57</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>No</t>
@@ -9951,7 +9991,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -9993,154 +10033,154 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Last 7 games: 6/24, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>7.87</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>45.42</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>90.54</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>101.6393</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.4266</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.1702</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.3322</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>73.41</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>36.51</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>36.04</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>21.26</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>83.89</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.2559</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.0609</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>37.53</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>88.98</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>98.7109</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>0.1598</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>0.3433</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>71.58</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>20.59</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>42.96</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>0.1658</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>8.65</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>37.12</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>88.27</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.3953</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.1607</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN11" t="inlineStr">
         <is>
           <t>72</t>
@@ -10152,56 +10192,16 @@
         </is>
       </c>
       <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10921,7 +10921,7 @@
         <v>50.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -10935,14 +10935,14 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>9</t>
@@ -10960,12 +10960,12 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.4</v>
+        <v>38.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11239,7 +11239,7 @@
         <v>50.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -11253,14 +11253,14 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>8</t>
@@ -11278,12 +11278,12 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-14.xlsx
@@ -910,34 +910,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1228,34 +1224,30 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1546,34 +1538,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1864,34 +1852,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2182,34 +2166,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2500,34 +2480,30 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,7 +2762,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2799,7 +2775,7 @@
         <v>50.1</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
@@ -2813,39 +2789,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3138,34 +3110,30 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3450,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3432,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3445,7 @@
         <v>50.1</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3491,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3768,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,7 +3746,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3795,7 +3759,7 @@
         <v>50.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -3809,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4037,12 +3997,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4067,7 +4027,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4086,7 +4046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,11 +4060,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>38.4</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -4113,13 +4073,13 @@
         <v>50.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4127,39 +4087,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4179,27 +4135,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,67 +4165,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -4355,12 +4311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4385,7 +4341,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4404,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,11 +4374,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -4431,13 +4387,13 @@
         <v>50.1</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>13.6</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4445,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4497,27 +4449,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,67 +4479,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4673,24 +4625,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -4703,17 +4655,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4736,26 +4688,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>20.2</v>
+        <v>47.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>37.5</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>50.1</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>60.7</v>
+        <v>13.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4768,34 +4720,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4815,127 +4763,127 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4991,12 +4939,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5021,7 +4969,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5040,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.1</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5058,22 +5006,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.7</v>
+        <v>37.5</v>
       </c>
       <c r="R15" t="n">
         <v>50.1</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>14.1</v>
+        <v>60.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5086,34 +5034,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,27 +5077,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,67 +5107,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.0168</t>
+          <t>98.7457</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.3662</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3084</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5309,24 +5253,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -5344,12 +5288,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,26 +5316,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>47.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R16" t="n">
         <v>50.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5399,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5451,12 +5391,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,112 +5406,112 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -5627,12 +5567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5657,7 +5597,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5676,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.2</v>
+        <v>29.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,26 +5630,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>50.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5717,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5769,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5784,12 +5720,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5799,67 +5735,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5945,12 +5881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5975,7 +5911,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,11 +5944,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -6021,13 +5957,13 @@
         <v>50.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,42 +5971,38 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -6087,12 +6019,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,7 +6034,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -6117,67 +6049,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6263,12 +6195,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6293,7 +6225,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6312,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6326,26 +6258,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
         <v>50.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6353,42 +6285,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -6405,7 +6333,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -6420,12 +6348,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6435,67 +6363,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -7082,34 +7010,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7400,34 +7324,30 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7718,34 +7638,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8036,34 +7952,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8354,34 +8266,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8672,34 +8580,30 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8944,7 +8848,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8958,7 +8862,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -8971,7 +8875,7 @@
         <v>50.1</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
@@ -8985,39 +8889,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9310,34 +9210,30 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9622,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9532,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9545,7 @@
         <v>50.1</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -9663,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9940,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,7 +9846,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9967,7 +9859,7 @@
         <v>50.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -9981,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10209,12 +10097,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10239,7 +10127,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10258,7 +10146,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,11 +10160,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>38.4</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -10285,13 +10173,13 @@
         <v>50.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10299,39 +10187,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10351,27 +10235,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10381,67 +10265,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -10527,12 +10411,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10557,7 +10441,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10576,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,11 +10474,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -10603,13 +10487,13 @@
         <v>50.1</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>13.6</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10617,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10669,27 +10549,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,67 +10579,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10845,24 +10725,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -10875,17 +10755,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10908,26 +10788,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>20.2</v>
+        <v>47.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>37.5</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>50.1</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>60.7</v>
+        <v>13.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10940,34 +10820,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10987,127 +10863,127 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -11163,12 +11039,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11193,7 +11069,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11212,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.1</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11230,22 +11106,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.7</v>
+        <v>37.5</v>
       </c>
       <c r="R15" t="n">
         <v>50.1</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>14.1</v>
+        <v>60.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11258,34 +11134,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,27 +11177,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,67 +11207,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.0168</t>
+          <t>98.7457</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.3662</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3084</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11481,24 +11353,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -11516,12 +11388,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11530,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,26 +11416,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>47.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R16" t="n">
         <v>50.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11571,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11623,12 +11491,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,112 +11506,112 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -11799,12 +11667,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11829,7 +11697,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11848,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.2</v>
+        <v>29.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,26 +11730,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>50.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11889,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11941,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11956,12 +11820,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11971,67 +11835,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12117,12 +11981,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12147,7 +12011,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,11 +12044,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -12193,13 +12057,13 @@
         <v>50.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,42 +12071,38 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -12259,12 +12119,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,7 +12134,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -12289,67 +12149,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12435,12 +12295,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12465,7 +12325,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12484,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12498,26 +12358,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
         <v>50.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12525,42 +12385,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -12577,7 +12433,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -12592,12 +12448,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12607,67 +12463,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
